--- a/Results/Comparison - Arousal.xlsx
+++ b/Results/Comparison - Arousal.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nikoo\Desktop\Thesis\Source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCBB1ABA-F47B-4078-8674-3BB6CAB56436}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7D28A4C-C36D-4137-94B8-D0B40434501C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{8D592C9F-CC51-43DD-B2E3-0BF015735963}"/>
   </bookViews>
@@ -172,7 +172,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -181,13 +181,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79998168889431442"/>
+        <fgColor rgb="FFFFFF66"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -376,7 +370,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -385,72 +379,83 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -468,22 +473,35 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -492,6 +510,12 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FFFFFF66"/>
+      <color rgb="FFCCFF66"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -877,28 +901,28 @@
         <v>12</v>
       </c>
       <c r="D2">
-        <v>0.463501291989664</v>
+        <v>0.58179217423403395</v>
       </c>
       <c r="E2">
-        <v>0.23302288116816799</v>
+        <v>0.19825034349200299</v>
       </c>
       <c r="F2">
-        <v>0.24318691644272999</v>
+        <v>0.315987759011014</v>
       </c>
       <c r="G2">
-        <v>0.27482705551823799</v>
+        <v>0.29705813199457198</v>
       </c>
       <c r="H2">
-        <v>0.30413436692506401</v>
+        <v>0.41345514950166101</v>
       </c>
       <c r="I2">
-        <v>0.37623640397533498</v>
+        <v>0.40477033530433598</v>
       </c>
       <c r="J2">
-        <v>0.29088224437061599</v>
+        <v>0.35326688815060903</v>
       </c>
       <c r="K2">
-        <v>0.35915020236176798</v>
+        <v>0.37063176709575701</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
@@ -909,31 +933,31 @@
         <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D3">
-        <v>0.54554263565891403</v>
+        <v>0.58480066445182699</v>
       </c>
       <c r="E3">
-        <v>0.210727534313052</v>
+        <v>0.23329011445622899</v>
       </c>
       <c r="F3">
-        <v>0.18643578643578601</v>
+        <v>0.28344407530454002</v>
       </c>
       <c r="G3">
-        <v>0.21046455686173701</v>
+        <v>0.29875849708199498</v>
       </c>
       <c r="H3">
-        <v>0.31937984496124</v>
+        <v>0.40271317829457298</v>
       </c>
       <c r="I3">
-        <v>0.38970820317871402</v>
+        <v>0.433540949556799</v>
       </c>
       <c r="J3">
-        <v>0.17111480251015099</v>
+        <v>0.27959579180509397</v>
       </c>
       <c r="K3">
-        <v>0.22590086499245701</v>
+        <v>0.332664510690106</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
@@ -947,28 +971,28 @@
         <v>14</v>
       </c>
       <c r="D4">
-        <v>0.45542635658914699</v>
+        <v>0.58143226282761096</v>
       </c>
       <c r="E4">
-        <v>0.21071119598594801</v>
+        <v>0.21387296628095701</v>
       </c>
       <c r="F4">
-        <v>0.163929997650927</v>
+        <v>0.17906976744186001</v>
       </c>
       <c r="G4">
-        <v>0.194857797842407</v>
+        <v>0.231442558272343</v>
       </c>
       <c r="H4">
-        <v>0.24677002583979299</v>
+        <v>0.30232558139534799</v>
       </c>
       <c r="I4">
-        <v>0.340768145974853</v>
+        <v>0.40067097140932001</v>
       </c>
       <c r="J4">
-        <v>0.18080472499077099</v>
+        <v>0.16561461794019899</v>
       </c>
       <c r="K4">
-        <v>0.25124689815484802</v>
+        <v>0.25536073540239201</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
@@ -979,31 +1003,31 @@
         <v>15</v>
       </c>
       <c r="C5" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D5">
-        <v>0.49386304909560702</v>
+        <v>0.557991878922111</v>
       </c>
       <c r="E5">
-        <v>0.243054214200458</v>
+        <v>0.21608948154482999</v>
       </c>
       <c r="F5">
-        <v>0.13524950501694599</v>
+        <v>0.13464881371858101</v>
       </c>
       <c r="G5">
-        <v>0.200660764931722</v>
+        <v>0.230773038409925</v>
       </c>
       <c r="H5">
-        <v>0.201771871539313</v>
+        <v>0.241085271317829</v>
       </c>
       <c r="I5">
-        <v>0.33589393535374901</v>
+        <v>0.40384695397866499</v>
       </c>
       <c r="J5">
-        <v>0.153617571059431</v>
+        <v>0.133803986710963</v>
       </c>
       <c r="K5">
-        <v>0.26433393376551401</v>
+        <v>0.26780898293945998</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
@@ -1014,31 +1038,31 @@
         <v>18</v>
       </c>
       <c r="C6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D6">
-        <v>0.55038759689922401</v>
+        <v>0.57668881506090797</v>
       </c>
       <c r="E6">
-        <v>0.238371217689897</v>
+        <v>0.16441898511569</v>
       </c>
       <c r="F6">
-        <v>0.207489409814991</v>
+        <v>0.293630658746937</v>
       </c>
       <c r="G6">
-        <v>0.24468419289691301</v>
+        <v>0.27395147647380702</v>
       </c>
       <c r="H6">
-        <v>0.29533038021410102</v>
+        <v>0.430620155038759</v>
       </c>
       <c r="I6">
-        <v>0.37016733999763901</v>
+        <v>0.41384205741159602</v>
       </c>
       <c r="J6">
-        <v>0.25443890734588398</v>
+        <v>0.29858803986710902</v>
       </c>
       <c r="K6">
-        <v>0.34458028555167902</v>
+        <v>0.32348581384518299</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
@@ -1049,31 +1073,31 @@
         <v>18</v>
       </c>
       <c r="C7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D7">
-        <v>0.50645994832041297</v>
+        <v>0.58877814691768104</v>
       </c>
       <c r="E7">
-        <v>0.22897031438631199</v>
+        <v>0.223506911271037</v>
       </c>
       <c r="F7">
-        <v>0.20612604449813701</v>
+        <v>0.24306520353031899</v>
       </c>
       <c r="G7">
-        <v>0.227162484209358</v>
+        <v>0.295861648792964</v>
       </c>
       <c r="H7">
-        <v>0.26090808416389799</v>
+        <v>0.36899224806201503</v>
       </c>
       <c r="I7">
-        <v>0.328926025839618</v>
+        <v>0.43629846295525299</v>
       </c>
       <c r="J7">
-        <v>0.246557770394979</v>
+        <v>0.220265780730897</v>
       </c>
       <c r="K7">
-        <v>0.31851070599408199</v>
+        <v>0.30410436666768198</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
@@ -1084,31 +1108,31 @@
         <v>18</v>
       </c>
       <c r="C8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D8">
-        <v>0.44961240310077499</v>
+        <v>0.58392395717977097</v>
       </c>
       <c r="E8">
-        <v>0.23594999929222699</v>
+        <v>0.212597346488196</v>
       </c>
       <c r="F8">
-        <v>0.20045561673468601</v>
+        <v>0.181155407899593</v>
       </c>
       <c r="G8">
-        <v>0.25793367106126702</v>
+        <v>0.236608071947846</v>
       </c>
       <c r="H8">
-        <v>0.253036175710594</v>
+        <v>0.31550387596899199</v>
       </c>
       <c r="I8">
-        <v>0.35108310037422602</v>
+        <v>0.40877638278394601</v>
       </c>
       <c r="J8">
-        <v>0.240817644887412</v>
+        <v>0.168355481727574</v>
       </c>
       <c r="K8">
-        <v>0.33313690161090898</v>
+        <v>0.26097845763543198</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
@@ -1119,31 +1143,31 @@
         <v>18</v>
       </c>
       <c r="C9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D9">
-        <v>0.52713178294573604</v>
+        <v>0.566205241786637</v>
       </c>
       <c r="E9">
-        <v>0.268012348882465</v>
+        <v>0.235938054931492</v>
       </c>
       <c r="F9">
-        <v>0.13701466492164099</v>
+        <v>0.17705795496493101</v>
       </c>
       <c r="G9">
-        <v>0.22948387661765199</v>
+        <v>0.223208000088915</v>
       </c>
       <c r="H9">
-        <v>0.18045404208194901</v>
+        <v>0.35542635658914701</v>
       </c>
       <c r="I9">
-        <v>0.31078394060606102</v>
+        <v>0.44542928413006999</v>
       </c>
       <c r="J9">
-        <v>0.16805094130675499</v>
+        <v>0.15456810631229201</v>
       </c>
       <c r="K9">
-        <v>0.30961387332588303</v>
+        <v>0.225980395859705</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.3">
@@ -1154,31 +1178,31 @@
         <v>18</v>
       </c>
       <c r="C10" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D10">
-        <v>0.53687806182417297</v>
+        <v>0.62126173882786395</v>
       </c>
       <c r="E10">
-        <v>0.19765766856081801</v>
+        <v>0.22486412164074601</v>
       </c>
       <c r="F10">
-        <v>0.25349457209216397</v>
+        <v>0.16491644217651899</v>
       </c>
       <c r="G10">
-        <v>0.20106840040254501</v>
+        <v>0.22777011808991801</v>
       </c>
       <c r="H10">
-        <v>0.37579459752467897</v>
+        <v>0.26151950524655498</v>
       </c>
       <c r="I10">
-        <v>0.33341777308293302</v>
+        <v>0.36306776862044499</v>
       </c>
       <c r="J10">
-        <v>0.26656608215791</v>
+        <v>0.21666641295574199</v>
       </c>
       <c r="K10">
-        <v>0.23003198024580301</v>
+        <v>0.335769133543252</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.3">
@@ -1192,28 +1216,28 @@
         <v>12</v>
       </c>
       <c r="D11">
-        <v>0.53925733114508201</v>
+        <v>0.61295232314833004</v>
       </c>
       <c r="E11">
-        <v>0.304752586007281</v>
+        <v>0.25084020454906197</v>
       </c>
       <c r="F11">
-        <v>0.25252095008907299</v>
+        <v>0.15690725310655501</v>
       </c>
       <c r="G11">
-        <v>0.33910914458570202</v>
+        <v>0.21561463977043399</v>
       </c>
       <c r="H11">
-        <v>0.22965821489823801</v>
+        <v>0.21244095473114599</v>
       </c>
       <c r="I11">
-        <v>0.31433691956260001</v>
+        <v>0.31708340638460403</v>
       </c>
       <c r="J11">
-        <v>0.34566487601229701</v>
+        <v>0.202504631078502</v>
       </c>
       <c r="K11">
-        <v>0.44246880542634998</v>
+        <v>0.308790168457032</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.3">
@@ -1227,28 +1251,28 @@
         <v>14</v>
       </c>
       <c r="D12">
-        <v>0.53614907769228004</v>
+        <v>0.62957251619449295</v>
       </c>
       <c r="E12">
-        <v>0.16086280092303401</v>
+        <v>0.22218406508268801</v>
       </c>
       <c r="F12">
-        <v>0.25229402678720098</v>
+        <v>0.12053210539075</v>
       </c>
       <c r="G12">
-        <v>0.16521439464454199</v>
+        <v>0.15169010555742801</v>
       </c>
       <c r="H12">
-        <v>0.37651021029352</v>
+        <v>0.21377976029138801</v>
       </c>
       <c r="I12">
-        <v>0.33071716342726798</v>
+        <v>0.28419160824453799</v>
       </c>
       <c r="J12">
-        <v>0.25939386641190398</v>
+        <v>0.13961806181008399</v>
       </c>
       <c r="K12">
-        <v>0.16956289246994999</v>
+        <v>0.247801300451089</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
@@ -1259,31 +1283,31 @@
         <v>18</v>
       </c>
       <c r="C13" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D13">
-        <v>0.54274366693563902</v>
+        <v>0.64887074474477202</v>
       </c>
       <c r="E13">
-        <v>0.246067101818016</v>
+        <v>0.239827768735762</v>
       </c>
       <c r="F13">
-        <v>0.23204658825397101</v>
+        <v>0.11017090354096599</v>
       </c>
       <c r="G13">
-        <v>0.26372030494170001</v>
+        <v>0.15171805256356399</v>
       </c>
       <c r="H13">
-        <v>0.27485741269021102</v>
+        <v>0.25293466223698702</v>
       </c>
       <c r="I13">
-        <v>0.30835946702184702</v>
+        <v>0.364227655970775</v>
       </c>
       <c r="J13">
-        <v>0.27869510705106099</v>
+        <v>0.11591771481612299</v>
       </c>
       <c r="K13">
-        <v>0.33205065589931698</v>
+        <v>0.223570214789473</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
@@ -1297,28 +1321,28 @@
         <v>12</v>
       </c>
       <c r="D14">
-        <v>0.53787285217324199</v>
+        <v>0.62444014836872097</v>
       </c>
       <c r="E14">
-        <v>0.31797600629444001</v>
+        <v>0.23231752113617499</v>
       </c>
       <c r="F14">
-        <v>0.25983671864391999</v>
+        <v>0.16698164642937299</v>
       </c>
       <c r="G14">
-        <v>0.34314109579655999</v>
+        <v>0.23388375897007299</v>
       </c>
       <c r="H14">
-        <v>0.26055785197699799</v>
+        <v>0.20526444153758799</v>
       </c>
       <c r="I14">
-        <v>0.33195517091080801</v>
+        <v>0.29873931029970602</v>
       </c>
       <c r="J14">
-        <v>0.35390727248500797</v>
+        <v>0.200376891457062</v>
       </c>
       <c r="K14">
-        <v>0.44504058896418902</v>
+        <v>0.29489070379217203</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.3">
@@ -1329,31 +1353,31 @@
         <v>15</v>
       </c>
       <c r="C15" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D15">
-        <v>0.52148495325755195</v>
+        <v>0.62024594417771095</v>
       </c>
       <c r="E15">
-        <v>0.157425012343926</v>
+        <v>0.21867884881458099</v>
       </c>
       <c r="F15">
-        <v>0.243830243253296</v>
+        <v>0.16205034625891601</v>
       </c>
       <c r="G15">
-        <v>0.18924798166338999</v>
+        <v>0.20558627084284201</v>
       </c>
       <c r="H15">
-        <v>0.36112464854381598</v>
+        <v>0.26056373834723601</v>
       </c>
       <c r="I15">
-        <v>0.33096824861783603</v>
+        <v>0.34485634071936</v>
       </c>
       <c r="J15">
-        <v>0.25401865352641301</v>
+        <v>0.18828386895382301</v>
       </c>
       <c r="K15">
-        <v>0.20516285211132099</v>
+        <v>0.28127340855673999</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">
@@ -1367,28 +1391,28 @@
         <v>11</v>
       </c>
       <c r="D16">
-        <v>0.53911987225616598</v>
+        <v>0.65070979433828502</v>
       </c>
       <c r="E16">
-        <v>0.21776574023187201</v>
+        <v>0.21170234940938501</v>
       </c>
       <c r="F16">
-        <v>0.24006573252362601</v>
+        <v>0.16188975216802901</v>
       </c>
       <c r="G16">
-        <v>0.21352391570336399</v>
+        <v>0.21450280384525999</v>
       </c>
       <c r="H16">
-        <v>0.37343227172183202</v>
+        <v>0.30797509983556498</v>
       </c>
       <c r="I16">
-        <v>0.345194415291742</v>
+        <v>0.37957981279063902</v>
       </c>
       <c r="J16">
-        <v>0.237583593489685</v>
+        <v>0.15990997629794501</v>
       </c>
       <c r="K16">
-        <v>0.23775521033795599</v>
+        <v>0.26055863836096399</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.3">
@@ -1399,31 +1423,31 @@
         <v>15</v>
       </c>
       <c r="C17" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D17">
-        <v>0.55715266961272403</v>
+        <v>0.65727093106758305</v>
       </c>
       <c r="E17">
-        <v>0.25929357383070201</v>
+        <v>0.21911289043579801</v>
       </c>
       <c r="F17">
-        <v>0.23089237583380101</v>
+        <v>0.14812494540551499</v>
       </c>
       <c r="G17">
-        <v>0.28931864521544698</v>
+        <v>0.174483928029735</v>
       </c>
       <c r="H17">
-        <v>0.247917729717302</v>
+        <v>0.28696013289036498</v>
       </c>
       <c r="I17">
-        <v>0.314645470878606</v>
+        <v>0.34606546842382102</v>
       </c>
       <c r="J17">
-        <v>0.28242335648944999</v>
+        <v>0.13943832162296399</v>
       </c>
       <c r="K17">
-        <v>0.36312490689286497</v>
+        <v>0.201907349165873</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.3">
@@ -1437,28 +1461,28 @@
         <v>12</v>
       </c>
       <c r="D18">
-        <v>0.39534883720930197</v>
+        <v>0.60182724252491604</v>
       </c>
       <c r="E18">
-        <v>0.21739237846308199</v>
+        <v>0.183411961240243</v>
       </c>
       <c r="F18">
-        <v>0.236351116583674</v>
+        <v>0.33905422742632002</v>
       </c>
       <c r="G18">
-        <v>0.246760115797862</v>
+        <v>0.30452456011920398</v>
       </c>
       <c r="H18">
-        <v>0.278903654485049</v>
+        <v>0.45813953488372</v>
       </c>
       <c r="I18">
-        <v>0.31975604865773199</v>
+        <v>0.42176527163139599</v>
       </c>
       <c r="J18">
-        <v>0.31479328165374598</v>
+        <v>0.322729789590254</v>
       </c>
       <c r="K18">
-        <v>0.354863541232525</v>
+        <v>0.316917694775668</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.3">
@@ -1469,31 +1493,31 @@
         <v>19</v>
       </c>
       <c r="C19" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D19">
-        <v>0.54521963824289399</v>
+        <v>0.58142303433001097</v>
       </c>
       <c r="E19">
-        <v>0.227096357030695</v>
+        <v>0.20518640942559499</v>
       </c>
       <c r="F19">
-        <v>0.23393608975004301</v>
+        <v>0.286019665089432</v>
       </c>
       <c r="G19">
-        <v>0.26078582930201499</v>
+        <v>0.26719405119941297</v>
       </c>
       <c r="H19">
-        <v>0.34263565891472803</v>
+        <v>0.42093023255813899</v>
       </c>
       <c r="I19">
-        <v>0.39354123932423501</v>
+        <v>0.417372936663506</v>
       </c>
       <c r="J19">
-        <v>0.25596160944998098</v>
+        <v>0.31337209302325503</v>
       </c>
       <c r="K19">
-        <v>0.33756067274138402</v>
+        <v>0.34784243542968102</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.3">
@@ -1504,31 +1528,31 @@
         <v>19</v>
       </c>
       <c r="C20" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D20">
-        <v>0.52454780361757103</v>
+        <v>0.59012550756736804</v>
       </c>
       <c r="E20">
-        <v>0.22520680691990599</v>
+        <v>0.223766276745337</v>
       </c>
       <c r="F20">
-        <v>0.213779889361284</v>
+        <v>0.22674250813785601</v>
       </c>
       <c r="G20">
-        <v>0.25842963326653601</v>
+        <v>0.25987873506500098</v>
       </c>
       <c r="H20">
-        <v>0.28992248062015502</v>
+        <v>0.35542635658914701</v>
       </c>
       <c r="I20">
-        <v>0.360718840436763</v>
+        <v>0.42005169071344201</v>
       </c>
       <c r="J20">
-        <v>0.239525655223329</v>
+        <v>0.193217054263565</v>
       </c>
       <c r="K20">
-        <v>0.33812159178921403</v>
+        <v>0.23778267619218599</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.3">
@@ -1539,31 +1563,31 @@
         <v>19</v>
       </c>
       <c r="C21" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D21">
-        <v>0.50645994832041297</v>
+        <v>0.58261351052048704</v>
       </c>
       <c r="E21">
-        <v>0.270368710274487</v>
+        <v>0.23701399094083</v>
       </c>
       <c r="F21">
-        <v>0.138803315547501</v>
+        <v>0.178386858619416</v>
       </c>
       <c r="G21">
-        <v>0.21996951659392699</v>
+        <v>0.22069591570726399</v>
       </c>
       <c r="H21">
-        <v>0.15968992248062</v>
+        <v>0.31395348837209303</v>
       </c>
       <c r="I21">
-        <v>0.274291018384964</v>
+        <v>0.40059597450245599</v>
       </c>
       <c r="J21">
-        <v>0.17558139534883699</v>
+        <v>0.16738648947951201</v>
       </c>
       <c r="K21">
-        <v>0.304140225827706</v>
+        <v>0.25316396061007501</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.3">
@@ -1577,28 +1601,28 @@
         <v>12</v>
       </c>
       <c r="D22">
-        <v>0.42687744442700498</v>
+        <v>0.62668136970889199</v>
       </c>
       <c r="E22">
-        <v>0.16259319509398201</v>
+        <v>0.17074990585637201</v>
       </c>
       <c r="F22">
-        <v>0.34489743516084598</v>
+        <v>0.255326639656341</v>
       </c>
       <c r="G22">
-        <v>0.24889977813098399</v>
+        <v>0.242505084969901</v>
       </c>
       <c r="H22">
-        <v>0.37286869315608401</v>
+        <v>0.37783297214141698</v>
       </c>
       <c r="I22">
-        <v>0.32762262219022498</v>
+        <v>0.37802003490278802</v>
       </c>
       <c r="J22">
-        <v>0.48339728359145601</v>
+        <v>0.26479332078097201</v>
       </c>
       <c r="K22">
-        <v>0.32752083760267497</v>
+        <v>0.28692729677768702</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.3">
@@ -1609,31 +1633,31 @@
         <v>19</v>
       </c>
       <c r="C23" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D23">
-        <v>0.54889729381781505</v>
+        <v>0.62656858437937801</v>
       </c>
       <c r="E23">
-        <v>0.153654340520191</v>
+        <v>0.19594537593548</v>
       </c>
       <c r="F23">
-        <v>0.25251673663505397</v>
+        <v>0.22802900603902601</v>
       </c>
       <c r="G23">
-        <v>0.172925516746159</v>
+        <v>0.23753281315185601</v>
       </c>
       <c r="H23">
-        <v>0.371785421813773</v>
+        <v>0.32261473256865297</v>
       </c>
       <c r="I23">
-        <v>0.33289738806484298</v>
+        <v>0.36526348781983198</v>
       </c>
       <c r="J23">
-        <v>0.24811130090353001</v>
+        <v>0.25323732977901697</v>
       </c>
       <c r="K23">
-        <v>0.175434737285278</v>
+        <v>0.300237873583308</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.3">
@@ -1644,31 +1668,31 @@
         <v>19</v>
       </c>
       <c r="C24" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D24">
-        <v>0.47576667754447199</v>
+        <v>0.65105266937994799</v>
       </c>
       <c r="E24">
-        <v>0.18606498428173601</v>
+        <v>0.212460990145036</v>
       </c>
       <c r="F24">
-        <v>0.25143402241699497</v>
+        <v>0.14016395750996799</v>
       </c>
       <c r="G24">
-        <v>0.20850766853486699</v>
+        <v>0.16889627409338001</v>
       </c>
       <c r="H24">
-        <v>0.35891687537124101</v>
+        <v>0.285206718346253</v>
       </c>
       <c r="I24">
-        <v>0.33460916330511897</v>
+        <v>0.34495770368873402</v>
       </c>
       <c r="J24">
-        <v>0.30196113020826099</v>
+        <v>0.105628259003232</v>
       </c>
       <c r="K24">
-        <v>0.264800832541916</v>
+        <v>0.131533570569907</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.3">
@@ -1682,28 +1706,28 @@
         <v>11</v>
       </c>
       <c r="D25">
-        <v>0.55291668200560296</v>
+        <v>0.62712826214722595</v>
       </c>
       <c r="E25">
-        <v>0.19349349234714999</v>
+        <v>0.21433473476329201</v>
       </c>
       <c r="F25">
-        <v>0.22047866665797</v>
+        <v>0.125947308505448</v>
       </c>
       <c r="G25">
-        <v>0.17339382031059</v>
+        <v>0.14743572809626901</v>
       </c>
       <c r="H25">
-        <v>0.36432446976639699</v>
+        <v>0.24285714285714199</v>
       </c>
       <c r="I25">
-        <v>0.33048252781519899</v>
+        <v>0.32213239096076401</v>
       </c>
       <c r="J25">
-        <v>0.22030380114150899</v>
+        <v>0.113499611550227</v>
       </c>
       <c r="K25">
-        <v>0.18616480110133099</v>
+        <v>0.15114616381943</v>
       </c>
     </row>
   </sheetData>
@@ -1724,644 +1748,656 @@
     <col min="8" max="15" width="15.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" s="27" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D1" s="28" t="s">
+    <row r="1" spans="1:15" s="10" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D1" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="E1" s="28" t="s">
+      <c r="E1" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="F1" s="28" t="s">
+      <c r="F1" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="G1" s="28" t="s">
+      <c r="G1" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="H1" s="27" t="s">
+      <c r="H1" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I1" s="27" t="s">
+      <c r="I1" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="J1" s="27" t="s">
+      <c r="J1" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="K1" s="27" t="s">
+      <c r="K1" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="L1" s="27" t="s">
+      <c r="L1" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="M1" s="27" t="s">
+      <c r="M1" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="N1" s="27" t="s">
+      <c r="N1" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="O1" s="27" t="s">
+      <c r="O1" s="10" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="B2" s="29" t="s">
+      <c r="B2" s="19" t="s">
         <v>29</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="32" t="s">
         <v>25</v>
       </c>
-      <c r="D2" s="29" t="s">
+      <c r="D2" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="E2" s="30"/>
-      <c r="F2" s="30"/>
-      <c r="G2" s="31"/>
-      <c r="H2" s="32" t="s">
+      <c r="E2" s="33"/>
+      <c r="F2" s="33"/>
+      <c r="G2" s="34"/>
+      <c r="H2" s="35" t="s">
         <v>27</v>
       </c>
-      <c r="I2" s="33"/>
-      <c r="J2" s="33"/>
-      <c r="K2" s="34"/>
-      <c r="L2" s="32" t="s">
+      <c r="I2" s="36"/>
+      <c r="J2" s="36"/>
+      <c r="K2" s="37"/>
+      <c r="L2" s="35" t="s">
         <v>28</v>
       </c>
-      <c r="M2" s="33"/>
-      <c r="N2" s="33"/>
-      <c r="O2" s="34"/>
+      <c r="M2" s="36"/>
+      <c r="N2" s="36"/>
+      <c r="O2" s="37"/>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="B3" s="37"/>
-      <c r="C3" s="10" t="s">
+      <c r="B3" s="27"/>
+      <c r="C3" s="38" t="s">
         <v>20</v>
       </c>
-      <c r="D3" s="9" t="s">
+      <c r="D3" s="39" t="s">
         <v>21</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3" s="40" t="s">
         <v>22</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="F3" s="40" t="s">
         <v>23</v>
       </c>
-      <c r="G3" s="10" t="s">
+      <c r="G3" s="38" t="s">
         <v>24</v>
       </c>
-      <c r="H3" s="9" t="s">
+      <c r="H3" s="39" t="s">
         <v>21</v>
       </c>
-      <c r="I3" s="5" t="s">
+      <c r="I3" s="40" t="s">
         <v>22</v>
       </c>
-      <c r="J3" s="5" t="s">
+      <c r="J3" s="40" t="s">
         <v>23</v>
       </c>
-      <c r="K3" s="10" t="s">
+      <c r="K3" s="38" t="s">
         <v>24</v>
       </c>
-      <c r="L3" s="9" t="s">
+      <c r="L3" s="39" t="s">
         <v>21</v>
       </c>
-      <c r="M3" s="5" t="s">
+      <c r="M3" s="40" t="s">
         <v>22</v>
       </c>
-      <c r="N3" s="5" t="s">
+      <c r="N3" s="40" t="s">
         <v>23</v>
       </c>
-      <c r="O3" s="10" t="s">
+      <c r="O3" s="38" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A4" s="27" t="s">
+      <c r="A4" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="38" t="s">
+      <c r="B4" s="12" t="s">
         <v>30</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="13" t="str">
+      <c r="D4" s="6" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$D:$D,Sheet1!$C:$C,$C4,Sheet1!$B:$B,D$1,Sheet1!$A:$A,$A4)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$E:$E,Sheet1!$C:$C,$C4,Sheet1!$B:$B,D$1,Sheet1!$A:$A,$A4)*100,2),"0.00")</f>
-        <v>53.9120 ± 21.78</v>
-      </c>
-      <c r="E4" s="7" t="str">
+        <v>65.0710 ± 21.17</v>
+      </c>
+      <c r="E4" s="5" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$F:$F,Sheet1!$C:$C,$C4,Sheet1!$B:$B,E$1,Sheet1!$A:$A,$A4)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$G:$G,Sheet1!$C:$C,$C4,Sheet1!$B:$B,E$1,Sheet1!$A:$A,$A4)*100,2),"0.00")</f>
-        <v>24.0066 ± 21.35</v>
-      </c>
-      <c r="F4" s="6" t="str">
+        <v>16.1890 ± 21.45</v>
+      </c>
+      <c r="F4" s="4" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$H:$H,Sheet1!$C:$C,$C4,Sheet1!$B:$B,F$1,Sheet1!$A:$A,$A4)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$I:$I,Sheet1!$C:$C,$C4,Sheet1!$B:$B,F$1,Sheet1!$A:$A,$A4)*100,2),"0.00")</f>
-        <v>37.3432 ± 34.52</v>
-      </c>
-      <c r="G4" s="14" t="str">
+        <v>30.7975 ± 37.96</v>
+      </c>
+      <c r="G4" s="7" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$J:$J,Sheet1!$C:$C,$C4,Sheet1!$B:$B,G$1,Sheet1!$A:$A,$A4)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$K:$K,Sheet1!$C:$C,$C4,Sheet1!$B:$B,G$1,Sheet1!$A:$A,$A4)*100,2),"0.00")</f>
-        <v>23.7584 ± 23.78</v>
-      </c>
-      <c r="H4" s="18" t="str">
+        <v>15.9910 ± 26.06</v>
+      </c>
+      <c r="H4" s="6" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$D:$D,Sheet1!$C:$C,$C4,Sheet1!$B:$B,H$1,Sheet1!$A:$A,$A4)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$E:$E,Sheet1!$C:$C,$C4,Sheet1!$B:$B,H$1,Sheet1!$A:$A,$A4)*100,2),"0.00")</f>
-        <v>55.2917 ± 19.35</v>
-      </c>
-      <c r="I4" s="7" t="str">
+        <v>62.7128 ± 21.43</v>
+      </c>
+      <c r="I4" s="5" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$F:$F,Sheet1!$C:$C,$C4,Sheet1!$B:$B,I$1,Sheet1!$A:$A,$A4)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$G:$G,Sheet1!$C:$C,$C4,Sheet1!$B:$B,I$1,Sheet1!$A:$A,$A4)*100,2),"0.00")</f>
-        <v>22.0479 ± 17.34</v>
-      </c>
-      <c r="J4" s="7" t="str">
+        <v>12.5947 ± 14.74</v>
+      </c>
+      <c r="J4" s="5" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$H:$H,Sheet1!$C:$C,$C4,Sheet1!$B:$B,J$1,Sheet1!$A:$A,$A4)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$I:$I,Sheet1!$C:$C,$C4,Sheet1!$B:$B,J$1,Sheet1!$A:$A,$A4)*100,2),"0.00")</f>
-        <v>36.4324 ± 33.05</v>
-      </c>
-      <c r="K4" s="14" t="str">
+        <v>24.2857 ± 32.21</v>
+      </c>
+      <c r="K4" s="7" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$J:$J,Sheet1!$C:$C,$C4,Sheet1!$B:$B,K$1,Sheet1!$A:$A,$A4)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$K:$K,Sheet1!$C:$C,$C4,Sheet1!$B:$B,K$1,Sheet1!$A:$A,$A4)*100,2),"0.00")</f>
-        <v>22.0304 ± 18.62</v>
-      </c>
-      <c r="L4" s="13" t="str">
+        <v>11.3500 ± 15.11</v>
+      </c>
+      <c r="L4" s="8" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$D:$D,Sheet1!$C:$C,$C4,Sheet1!$B:$B,L$1,Sheet1!$A:$A,$A4)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$E:$E,Sheet1!$C:$C,$C4,Sheet1!$B:$B,L$1,Sheet1!$A:$A,$A4)*100,2),"0.00")</f>
-        <v>53.6878 ± 19.77</v>
-      </c>
-      <c r="M4" s="6" t="str">
+        <v>64.8871 ± 23.98</v>
+      </c>
+      <c r="M4" s="5" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$F:$F,Sheet1!$C:$C,$C4,Sheet1!$B:$B,M$1,Sheet1!$A:$A,$A4)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$G:$G,Sheet1!$C:$C,$C4,Sheet1!$B:$B,M$1,Sheet1!$A:$A,$A4)*100,2),"0.00")</f>
-        <v>25.3495 ± 20.11</v>
-      </c>
-      <c r="N4" s="7" t="str">
+        <v>11.0171 ± 15.17</v>
+      </c>
+      <c r="N4" s="5" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$H:$H,Sheet1!$C:$C,$C4,Sheet1!$B:$B,N$1,Sheet1!$A:$A,$A4)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$I:$I,Sheet1!$C:$C,$C4,Sheet1!$B:$B,N$1,Sheet1!$A:$A,$A4)*100,2),"0.00")</f>
-        <v>37.5795 ± 33.34</v>
-      </c>
-      <c r="O4" s="14" t="str">
+        <v>25.2935 ± 36.42</v>
+      </c>
+      <c r="O4" s="7" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$J:$J,Sheet1!$C:$C,$C4,Sheet1!$B:$B,O$1,Sheet1!$A:$A,$A4)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$K:$K,Sheet1!$C:$C,$C4,Sheet1!$B:$B,O$1,Sheet1!$A:$A,$A4)*100,2),"0.00")</f>
-        <v>26.6566 ± 23.00</v>
+        <v>11.5918 ± 22.36</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A5" s="27" t="s">
+      <c r="A5" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="B5" s="39"/>
-      <c r="C5" s="20" t="s">
+      <c r="B5" s="13"/>
+      <c r="C5" s="28" t="s">
         <v>13</v>
       </c>
-      <c r="D5" s="26" t="str">
+      <c r="D5" s="29" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$D:$D,Sheet1!$C:$C,$C5,Sheet1!$B:$B,D$1,Sheet1!$A:$A,$A5)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$E:$E,Sheet1!$C:$C,$C5,Sheet1!$B:$B,D$1,Sheet1!$A:$A,$A5)*100,2),"0.00")</f>
-        <v>55.7153 ± 25.93</v>
-      </c>
-      <c r="E5" s="8" t="str">
+        <v>62.0246 ± 21.87</v>
+      </c>
+      <c r="E5" s="30" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$F:$F,Sheet1!$C:$C,$C5,Sheet1!$B:$B,E$1,Sheet1!$A:$A,$A5)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$G:$G,Sheet1!$C:$C,$C5,Sheet1!$B:$B,E$1,Sheet1!$A:$A,$A5)*100,2),"0.00")</f>
-        <v>23.0892 ± 28.93</v>
-      </c>
-      <c r="F5" s="8" t="str">
+        <v>16.2050 ± 20.56</v>
+      </c>
+      <c r="F5" s="30" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$H:$H,Sheet1!$C:$C,$C5,Sheet1!$B:$B,F$1,Sheet1!$A:$A,$A5)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$I:$I,Sheet1!$C:$C,$C5,Sheet1!$B:$B,F$1,Sheet1!$A:$A,$A5)*100,2),"0.00")</f>
-        <v>24.7918 ± 31.46</v>
-      </c>
-      <c r="G5" s="12" t="str">
+        <v>26.0564 ± 34.49</v>
+      </c>
+      <c r="G5" s="31" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$J:$J,Sheet1!$C:$C,$C5,Sheet1!$B:$B,G$1,Sheet1!$A:$A,$A5)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$K:$K,Sheet1!$C:$C,$C5,Sheet1!$B:$B,G$1,Sheet1!$A:$A,$A5)*100,2),"0.00")</f>
-        <v>28.2423 ± 36.31</v>
-      </c>
-      <c r="H5" s="11" t="str">
+        <v>18.8284 ± 28.13</v>
+      </c>
+      <c r="H5" s="29" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$D:$D,Sheet1!$C:$C,$C5,Sheet1!$B:$B,H$1,Sheet1!$A:$A,$A5)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$E:$E,Sheet1!$C:$C,$C5,Sheet1!$B:$B,H$1,Sheet1!$A:$A,$A5)*100,2),"0.00")</f>
-        <v>47.5767 ± 18.61</v>
-      </c>
-      <c r="I5" s="8" t="str">
+        <v>62.6569 ± 19.59</v>
+      </c>
+      <c r="I5" s="30" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$F:$F,Sheet1!$C:$C,$C5,Sheet1!$B:$B,I$1,Sheet1!$A:$A,$A5)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$G:$G,Sheet1!$C:$C,$C5,Sheet1!$B:$B,I$1,Sheet1!$A:$A,$A5)*100,2),"0.00")</f>
-        <v>25.1434 ± 20.85</v>
-      </c>
-      <c r="J5" s="8" t="str">
+        <v>22.8029 ± 23.75</v>
+      </c>
+      <c r="J5" s="30" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$H:$H,Sheet1!$C:$C,$C5,Sheet1!$B:$B,J$1,Sheet1!$A:$A,$A5)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$I:$I,Sheet1!$C:$C,$C5,Sheet1!$B:$B,J$1,Sheet1!$A:$A,$A5)*100,2),"0.00")</f>
-        <v>35.8917 ± 33.46</v>
-      </c>
-      <c r="K5" s="12" t="str">
+        <v>32.2615 ± 36.53</v>
+      </c>
+      <c r="K5" s="31" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$J:$J,Sheet1!$C:$C,$C5,Sheet1!$B:$B,K$1,Sheet1!$A:$A,$A5)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$K:$K,Sheet1!$C:$C,$C5,Sheet1!$B:$B,K$1,Sheet1!$A:$A,$A5)*100,2),"0.00")</f>
-        <v>30.1961 ± 26.48</v>
-      </c>
-      <c r="L5" s="26" t="str">
+        <v>25.3237 ± 30.02</v>
+      </c>
+      <c r="L5" s="29" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$D:$D,Sheet1!$C:$C,$C5,Sheet1!$B:$B,L$1,Sheet1!$A:$A,$A5)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$E:$E,Sheet1!$C:$C,$C5,Sheet1!$B:$B,L$1,Sheet1!$A:$A,$A5)*100,2),"0.00")</f>
-        <v>54.2744 ± 24.61</v>
-      </c>
-      <c r="M5" s="8" t="str">
+        <v>62.1262 ± 22.49</v>
+      </c>
+      <c r="M5" s="41" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$F:$F,Sheet1!$C:$C,$C5,Sheet1!$B:$B,M$1,Sheet1!$A:$A,$A5)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$G:$G,Sheet1!$C:$C,$C5,Sheet1!$B:$B,M$1,Sheet1!$A:$A,$A5)*100,2),"0.00")</f>
-        <v>23.2047 ± 26.37</v>
-      </c>
-      <c r="N5" s="8" t="str">
+        <v>16.4916 ± 22.78</v>
+      </c>
+      <c r="N5" s="41" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$H:$H,Sheet1!$C:$C,$C5,Sheet1!$B:$B,N$1,Sheet1!$A:$A,$A5)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$I:$I,Sheet1!$C:$C,$C5,Sheet1!$B:$B,N$1,Sheet1!$A:$A,$A5)*100,2),"0.00")</f>
-        <v>27.4857 ± 30.84</v>
-      </c>
-      <c r="O5" s="12" t="str">
+        <v>26.1520 ± 36.31</v>
+      </c>
+      <c r="O5" s="42" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$J:$J,Sheet1!$C:$C,$C5,Sheet1!$B:$B,O$1,Sheet1!$A:$A,$A5)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$K:$K,Sheet1!$C:$C,$C5,Sheet1!$B:$B,O$1,Sheet1!$A:$A,$A5)*100,2),"0.00")</f>
-        <v>27.8695 ± 33.21</v>
+        <v>21.6666 ± 33.58</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A6" s="27" t="s">
+      <c r="A6" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="B6" s="39"/>
+      <c r="B6" s="13"/>
       <c r="C6" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D6" s="13" t="str">
+      <c r="D6" s="6" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$D:$D,Sheet1!$C:$C,$C6,Sheet1!$B:$B,D$1,Sheet1!$A:$A,$A6)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$E:$E,Sheet1!$C:$C,$C6,Sheet1!$B:$B,D$1,Sheet1!$A:$A,$A6)*100,2),"0.00")</f>
-        <v>53.7873 ± 31.80</v>
-      </c>
-      <c r="E6" s="6" t="str">
+        <v>62.4440 ± 23.23</v>
+      </c>
+      <c r="E6" s="4" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$F:$F,Sheet1!$C:$C,$C6,Sheet1!$B:$B,E$1,Sheet1!$A:$A,$A6)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$G:$G,Sheet1!$C:$C,$C6,Sheet1!$B:$B,E$1,Sheet1!$A:$A,$A6)*100,2),"0.00")</f>
-        <v>25.9837 ± 34.31</v>
-      </c>
-      <c r="F6" s="7" t="str">
+        <v>16.6982 ± 23.39</v>
+      </c>
+      <c r="F6" s="5" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$H:$H,Sheet1!$C:$C,$C6,Sheet1!$B:$B,F$1,Sheet1!$A:$A,$A6)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$I:$I,Sheet1!$C:$C,$C6,Sheet1!$B:$B,F$1,Sheet1!$A:$A,$A6)*100,2),"0.00")</f>
-        <v>26.0558 ± 33.20</v>
-      </c>
-      <c r="G6" s="19" t="str">
+        <v>20.5264 ± 29.87</v>
+      </c>
+      <c r="G6" s="9" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$J:$J,Sheet1!$C:$C,$C6,Sheet1!$B:$B,G$1,Sheet1!$A:$A,$A6)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$K:$K,Sheet1!$C:$C,$C6,Sheet1!$B:$B,G$1,Sheet1!$A:$A,$A6)*100,2),"0.00")</f>
-        <v>35.3907 ± 44.50</v>
-      </c>
-      <c r="H6" s="13" t="str">
+        <v>20.0377 ± 29.49</v>
+      </c>
+      <c r="H6" s="6" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$D:$D,Sheet1!$C:$C,$C6,Sheet1!$B:$B,H$1,Sheet1!$A:$A,$A6)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$E:$E,Sheet1!$C:$C,$C6,Sheet1!$B:$B,H$1,Sheet1!$A:$A,$A6)*100,2),"0.00")</f>
-        <v>42.6877 ± 16.26</v>
-      </c>
-      <c r="I6" s="6" t="str">
+        <v>62.6681 ± 17.07</v>
+      </c>
+      <c r="I6" s="4" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$F:$F,Sheet1!$C:$C,$C6,Sheet1!$B:$B,I$1,Sheet1!$A:$A,$A6)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$G:$G,Sheet1!$C:$C,$C6,Sheet1!$B:$B,I$1,Sheet1!$A:$A,$A6)*100,2),"0.00")</f>
-        <v>34.4897 ± 24.89</v>
-      </c>
-      <c r="J6" s="6" t="str">
+        <v>25.5327 ± 24.25</v>
+      </c>
+      <c r="J6" s="4" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$H:$H,Sheet1!$C:$C,$C6,Sheet1!$B:$B,J$1,Sheet1!$A:$A,$A6)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$I:$I,Sheet1!$C:$C,$C6,Sheet1!$B:$B,J$1,Sheet1!$A:$A,$A6)*100,2),"0.00")</f>
-        <v>37.2869 ± 32.76</v>
-      </c>
-      <c r="K6" s="19" t="str">
+        <v>37.7833 ± 37.80</v>
+      </c>
+      <c r="K6" s="9" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$J:$J,Sheet1!$C:$C,$C6,Sheet1!$B:$B,K$1,Sheet1!$A:$A,$A6)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$K:$K,Sheet1!$C:$C,$C6,Sheet1!$B:$B,K$1,Sheet1!$A:$A,$A6)*100,2),"0.00")</f>
-        <v>48.3397 ± 32.75</v>
-      </c>
-      <c r="L6" s="13" t="str">
+        <v>26.4793 ± 28.69</v>
+      </c>
+      <c r="L6" s="6" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$D:$D,Sheet1!$C:$C,$C6,Sheet1!$B:$B,L$1,Sheet1!$A:$A,$A6)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$E:$E,Sheet1!$C:$C,$C6,Sheet1!$B:$B,L$1,Sheet1!$A:$A,$A6)*100,2),"0.00")</f>
-        <v>53.9257 ± 30.48</v>
-      </c>
-      <c r="M6" s="7" t="str">
+        <v>61.2952 ± 25.08</v>
+      </c>
+      <c r="M6" s="5" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$F:$F,Sheet1!$C:$C,$C6,Sheet1!$B:$B,M$1,Sheet1!$A:$A,$A6)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$G:$G,Sheet1!$C:$C,$C6,Sheet1!$B:$B,M$1,Sheet1!$A:$A,$A6)*100,2),"0.00")</f>
-        <v>25.2521 ± 33.91</v>
-      </c>
-      <c r="N6" s="7" t="str">
+        <v>15.6907 ± 21.56</v>
+      </c>
+      <c r="N6" s="5" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$H:$H,Sheet1!$C:$C,$C6,Sheet1!$B:$B,N$1,Sheet1!$A:$A,$A6)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$I:$I,Sheet1!$C:$C,$C6,Sheet1!$B:$B,N$1,Sheet1!$A:$A,$A6)*100,2),"0.00")</f>
-        <v>22.9658 ± 31.43</v>
-      </c>
-      <c r="O6" s="19" t="str">
+        <v>21.2441 ± 31.71</v>
+      </c>
+      <c r="O6" s="7" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$J:$J,Sheet1!$C:$C,$C6,Sheet1!$B:$B,O$1,Sheet1!$A:$A,$A6)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$K:$K,Sheet1!$C:$C,$C6,Sheet1!$B:$B,O$1,Sheet1!$A:$A,$A6)*100,2),"0.00")</f>
-        <v>34.5665 ± 44.25</v>
+        <v>20.2505 ± 30.88</v>
       </c>
     </row>
     <row r="7" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="27" t="s">
+      <c r="A7" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="B7" s="40"/>
-      <c r="C7" s="21" t="s">
+      <c r="B7" s="14"/>
+      <c r="C7" s="43" t="s">
         <v>14</v>
       </c>
-      <c r="D7" s="15" t="str">
+      <c r="D7" s="44" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$D:$D,Sheet1!$C:$C,$C7,Sheet1!$B:$B,D$1,Sheet1!$A:$A,$A7)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$E:$E,Sheet1!$C:$C,$C7,Sheet1!$B:$B,D$1,Sheet1!$A:$A,$A7)*100,2),"0.00")</f>
-        <v>52.1485 ± 15.74</v>
-      </c>
-      <c r="E7" s="16" t="str">
+        <v>65.7271 ± 21.91</v>
+      </c>
+      <c r="E7" s="45" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$F:$F,Sheet1!$C:$C,$C7,Sheet1!$B:$B,E$1,Sheet1!$A:$A,$A7)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$G:$G,Sheet1!$C:$C,$C7,Sheet1!$B:$B,E$1,Sheet1!$A:$A,$A7)*100,2),"0.00")</f>
-        <v>24.3830 ± 18.92</v>
-      </c>
-      <c r="F7" s="16" t="str">
+        <v>14.8125 ± 17.45</v>
+      </c>
+      <c r="F7" s="45" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$H:$H,Sheet1!$C:$C,$C7,Sheet1!$B:$B,F$1,Sheet1!$A:$A,$A7)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$I:$I,Sheet1!$C:$C,$C7,Sheet1!$B:$B,F$1,Sheet1!$A:$A,$A7)*100,2),"0.00")</f>
-        <v>36.1125 ± 33.10</v>
-      </c>
-      <c r="G7" s="17" t="str">
+        <v>28.6960 ± 34.61</v>
+      </c>
+      <c r="G7" s="46" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$J:$J,Sheet1!$C:$C,$C7,Sheet1!$B:$B,G$1,Sheet1!$A:$A,$A7)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$K:$K,Sheet1!$C:$C,$C7,Sheet1!$B:$B,G$1,Sheet1!$A:$A,$A7)*100,2),"0.00")</f>
-        <v>25.4019 ± 20.52</v>
-      </c>
-      <c r="H7" s="15" t="str">
+        <v>13.9438 ± 20.19</v>
+      </c>
+      <c r="H7" s="44" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$D:$D,Sheet1!$C:$C,$C7,Sheet1!$B:$B,H$1,Sheet1!$A:$A,$A7)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$E:$E,Sheet1!$C:$C,$C7,Sheet1!$B:$B,H$1,Sheet1!$A:$A,$A7)*100,2),"0.00")</f>
-        <v>54.8897 ± 15.37</v>
-      </c>
-      <c r="I7" s="16" t="str">
+        <v>65.1053 ± 21.25</v>
+      </c>
+      <c r="I7" s="45" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$F:$F,Sheet1!$C:$C,$C7,Sheet1!$B:$B,I$1,Sheet1!$A:$A,$A7)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$G:$G,Sheet1!$C:$C,$C7,Sheet1!$B:$B,I$1,Sheet1!$A:$A,$A7)*100,2),"0.00")</f>
-        <v>25.2517 ± 17.29</v>
-      </c>
-      <c r="J7" s="16" t="str">
+        <v>14.0164 ± 16.89</v>
+      </c>
+      <c r="J7" s="45" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$H:$H,Sheet1!$C:$C,$C7,Sheet1!$B:$B,J$1,Sheet1!$A:$A,$A7)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$I:$I,Sheet1!$C:$C,$C7,Sheet1!$B:$B,J$1,Sheet1!$A:$A,$A7)*100,2),"0.00")</f>
-        <v>37.1785 ± 33.29</v>
-      </c>
-      <c r="K7" s="17" t="str">
+        <v>28.5207 ± 34.50</v>
+      </c>
+      <c r="K7" s="46" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$J:$J,Sheet1!$C:$C,$C7,Sheet1!$B:$B,K$1,Sheet1!$A:$A,$A7)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$K:$K,Sheet1!$C:$C,$C7,Sheet1!$B:$B,K$1,Sheet1!$A:$A,$A7)*100,2),"0.00")</f>
-        <v>24.8111 ± 17.54</v>
-      </c>
-      <c r="L7" s="15" t="str">
+        <v>10.5628 ± 13.15</v>
+      </c>
+      <c r="L7" s="47" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$D:$D,Sheet1!$C:$C,$C7,Sheet1!$B:$B,L$1,Sheet1!$A:$A,$A7)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$E:$E,Sheet1!$C:$C,$C7,Sheet1!$B:$B,L$1,Sheet1!$A:$A,$A7)*100,2),"0.00")</f>
-        <v>53.6149 ± 16.09</v>
-      </c>
-      <c r="M7" s="16" t="str">
+        <v>62.9573 ± 22.22</v>
+      </c>
+      <c r="M7" s="45" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$F:$F,Sheet1!$C:$C,$C7,Sheet1!$B:$B,M$1,Sheet1!$A:$A,$A7)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$G:$G,Sheet1!$C:$C,$C7,Sheet1!$B:$B,M$1,Sheet1!$A:$A,$A7)*100,2),"0.00")</f>
-        <v>25.2294 ± 16.52</v>
-      </c>
-      <c r="N7" s="25" t="str">
+        <v>12.0532 ± 15.17</v>
+      </c>
+      <c r="N7" s="45" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$H:$H,Sheet1!$C:$C,$C7,Sheet1!$B:$B,N$1,Sheet1!$A:$A,$A7)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$I:$I,Sheet1!$C:$C,$C7,Sheet1!$B:$B,N$1,Sheet1!$A:$A,$A7)*100,2),"0.00")</f>
-        <v>37.6510 ± 33.07</v>
-      </c>
-      <c r="O7" s="17" t="str">
+        <v>21.3780 ± 28.42</v>
+      </c>
+      <c r="O7" s="46" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$J:$J,Sheet1!$C:$C,$C7,Sheet1!$B:$B,O$1,Sheet1!$A:$A,$A7)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$K:$K,Sheet1!$C:$C,$C7,Sheet1!$B:$B,O$1,Sheet1!$A:$A,$A7)*100,2),"0.00")</f>
-        <v>25.9394 ± 16.96</v>
+        <v>13.9618 ± 24.78</v>
       </c>
     </row>
     <row r="8" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="27"/>
+      <c r="A8" s="10"/>
       <c r="B8" s="1"/>
+      <c r="D8" s="17"/>
+      <c r="E8" s="17"/>
+      <c r="F8" s="17"/>
+      <c r="G8" s="17"/>
+      <c r="H8" s="18"/>
+      <c r="I8" s="18"/>
+      <c r="J8" s="18"/>
+      <c r="K8" s="18"/>
+      <c r="L8" s="18"/>
+      <c r="M8" s="18"/>
+      <c r="N8" s="18"/>
+      <c r="O8" s="18"/>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A9" s="27"/>
-      <c r="B9" s="29" t="s">
+      <c r="A9" s="10"/>
+      <c r="B9" s="19" t="s">
         <v>29</v>
       </c>
-      <c r="C9" s="22" t="s">
+      <c r="C9" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="D9" s="29" t="s">
+      <c r="D9" s="21" t="s">
         <v>26</v>
       </c>
-      <c r="E9" s="30"/>
-      <c r="F9" s="30"/>
-      <c r="G9" s="31"/>
-      <c r="H9" s="32" t="s">
+      <c r="E9" s="22"/>
+      <c r="F9" s="22"/>
+      <c r="G9" s="23"/>
+      <c r="H9" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="I9" s="33"/>
-      <c r="J9" s="33"/>
-      <c r="K9" s="34"/>
-      <c r="L9" s="32" t="s">
+      <c r="I9" s="25"/>
+      <c r="J9" s="25"/>
+      <c r="K9" s="26"/>
+      <c r="L9" s="24" t="s">
         <v>28</v>
       </c>
-      <c r="M9" s="33"/>
-      <c r="N9" s="33"/>
-      <c r="O9" s="34"/>
+      <c r="M9" s="25"/>
+      <c r="N9" s="25"/>
+      <c r="O9" s="26"/>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A10" s="27"/>
-      <c r="B10" s="37"/>
-      <c r="C10" s="23" t="s">
+      <c r="A10" s="10"/>
+      <c r="B10" s="27"/>
+      <c r="C10" s="28" t="s">
         <v>20</v>
       </c>
-      <c r="D10" s="9" t="s">
+      <c r="D10" s="29" t="s">
         <v>21</v>
       </c>
-      <c r="E10" s="5" t="s">
+      <c r="E10" s="30" t="s">
         <v>22</v>
       </c>
-      <c r="F10" s="5" t="s">
+      <c r="F10" s="30" t="s">
         <v>23</v>
       </c>
-      <c r="G10" s="10" t="s">
+      <c r="G10" s="31" t="s">
         <v>24</v>
       </c>
-      <c r="H10" s="9" t="s">
+      <c r="H10" s="29" t="s">
         <v>21</v>
       </c>
-      <c r="I10" s="5" t="s">
+      <c r="I10" s="30" t="s">
         <v>22</v>
       </c>
-      <c r="J10" s="5" t="s">
+      <c r="J10" s="30" t="s">
         <v>23</v>
       </c>
-      <c r="K10" s="10" t="s">
+      <c r="K10" s="31" t="s">
         <v>24</v>
       </c>
-      <c r="L10" s="9" t="s">
+      <c r="L10" s="29" t="s">
         <v>21</v>
       </c>
-      <c r="M10" s="5" t="s">
+      <c r="M10" s="30" t="s">
         <v>22</v>
       </c>
-      <c r="N10" s="5" t="s">
+      <c r="N10" s="30" t="s">
         <v>23</v>
       </c>
-      <c r="O10" s="10" t="s">
+      <c r="O10" s="31" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A11" s="27" t="s">
+      <c r="A11" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="B11" s="35" t="s">
+      <c r="B11" s="15" t="s">
         <v>31</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D11" s="18" t="str">
+      <c r="D11" s="6" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$D:$D,Sheet1!$C:$C,$C11,Sheet1!$B:$B,D$1,Sheet1!$A:$A,$A11)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$E:$E,Sheet1!$C:$C,$C11,Sheet1!$B:$B,D$1,Sheet1!$A:$A,$A11)*100,2),"0.00")</f>
-        <v>54.5543 ± 21.07</v>
-      </c>
-      <c r="E11" s="7" t="str">
+        <v>55.7992 ± 21.61</v>
+      </c>
+      <c r="E11" s="5" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$F:$F,Sheet1!$C:$C,$C11,Sheet1!$B:$B,E$1,Sheet1!$A:$A,$A11)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$G:$G,Sheet1!$C:$C,$C11,Sheet1!$B:$B,E$1,Sheet1!$A:$A,$A11)*100,2),"0.00")</f>
-        <v>18.6436 ± 21.05</v>
-      </c>
-      <c r="F11" s="6" t="str">
+        <v>13.4649 ± 23.08</v>
+      </c>
+      <c r="F11" s="5" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$H:$H,Sheet1!$C:$C,$C11,Sheet1!$B:$B,F$1,Sheet1!$A:$A,$A11)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$I:$I,Sheet1!$C:$C,$C11,Sheet1!$B:$B,F$1,Sheet1!$A:$A,$A11)*100,2),"0.00")</f>
-        <v>31.9380 ± 38.97</v>
-      </c>
-      <c r="G11" s="14" t="str">
+        <v>24.1085 ± 40.38</v>
+      </c>
+      <c r="G11" s="7" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$J:$J,Sheet1!$C:$C,$C11,Sheet1!$B:$B,G$1,Sheet1!$A:$A,$A11)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$K:$K,Sheet1!$C:$C,$C11,Sheet1!$B:$B,G$1,Sheet1!$A:$A,$A11)*100,2),"0.00")</f>
-        <v>17.1115 ± 22.59</v>
-      </c>
-      <c r="H11" s="13" t="str">
+        <v>13.3804 ± 26.78</v>
+      </c>
+      <c r="H11" s="6" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$D:$D,Sheet1!$C:$C,$C11,Sheet1!$B:$B,H$1,Sheet1!$A:$A,$A11)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$E:$E,Sheet1!$C:$C,$C11,Sheet1!$B:$B,H$1,Sheet1!$A:$A,$A11)*100,2),"0.00")</f>
-        <v>52.4548 ± 22.52</v>
-      </c>
-      <c r="I11" s="7" t="str">
+        <v>58.1423 ± 20.52</v>
+      </c>
+      <c r="I11" s="5" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$F:$F,Sheet1!$C:$C,$C11,Sheet1!$B:$B,I$1,Sheet1!$A:$A,$A11)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$G:$G,Sheet1!$C:$C,$C11,Sheet1!$B:$B,I$1,Sheet1!$A:$A,$A11)*100,2),"0.00")</f>
-        <v>21.3780 ± 25.84</v>
-      </c>
-      <c r="J11" s="7" t="str">
+        <v>28.6020 ± 26.72</v>
+      </c>
+      <c r="J11" s="5" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$H:$H,Sheet1!$C:$C,$C11,Sheet1!$B:$B,J$1,Sheet1!$A:$A,$A11)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$I:$I,Sheet1!$C:$C,$C11,Sheet1!$B:$B,J$1,Sheet1!$A:$A,$A11)*100,2),"0.00")</f>
-        <v>28.9922 ± 36.07</v>
-      </c>
-      <c r="K11" s="14" t="str">
+        <v>42.0930 ± 41.74</v>
+      </c>
+      <c r="K11" s="7" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$J:$J,Sheet1!$C:$C,$C11,Sheet1!$B:$B,K$1,Sheet1!$A:$A,$A11)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$K:$K,Sheet1!$C:$C,$C11,Sheet1!$B:$B,K$1,Sheet1!$A:$A,$A11)*100,2),"0.00")</f>
-        <v>23.9526 ± 33.81</v>
-      </c>
-      <c r="L11" s="18" t="str">
+        <v>31.3372 ± 34.78</v>
+      </c>
+      <c r="L11" s="6" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$D:$D,Sheet1!$C:$C,$C11,Sheet1!$B:$B,L$1,Sheet1!$A:$A,$A11)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$E:$E,Sheet1!$C:$C,$C11,Sheet1!$B:$B,L$1,Sheet1!$A:$A,$A11)*100,2),"0.00")</f>
-        <v>55.0388 ± 23.84</v>
-      </c>
-      <c r="M11" s="6" t="str">
+        <v>58.3924 ± 21.26</v>
+      </c>
+      <c r="M11" s="5" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$F:$F,Sheet1!$C:$C,$C11,Sheet1!$B:$B,M$1,Sheet1!$A:$A,$A11)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$G:$G,Sheet1!$C:$C,$C11,Sheet1!$B:$B,M$1,Sheet1!$A:$A,$A11)*100,2),"0.00")</f>
-        <v>20.7489 ± 24.47</v>
-      </c>
-      <c r="N11" s="6" t="str">
+        <v>18.1155 ± 23.66</v>
+      </c>
+      <c r="N11" s="5" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$H:$H,Sheet1!$C:$C,$C11,Sheet1!$B:$B,N$1,Sheet1!$A:$A,$A11)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$I:$I,Sheet1!$C:$C,$C11,Sheet1!$B:$B,N$1,Sheet1!$A:$A,$A11)*100,2),"0.00")</f>
-        <v>29.5330 ± 37.02</v>
-      </c>
-      <c r="O11" s="19" t="str">
+        <v>31.5504 ± 40.88</v>
+      </c>
+      <c r="O11" s="7" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$J:$J,Sheet1!$C:$C,$C11,Sheet1!$B:$B,O$1,Sheet1!$A:$A,$A11)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$K:$K,Sheet1!$C:$C,$C11,Sheet1!$B:$B,O$1,Sheet1!$A:$A,$A11)*100,2),"0.00")</f>
-        <v>25.4439 ± 34.46</v>
+        <v>16.8355 ± 26.10</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A12" s="27" t="s">
+      <c r="A12" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="B12" s="35"/>
-      <c r="C12" s="20" t="s">
+      <c r="B12" s="15"/>
+      <c r="C12" s="28" t="s">
         <v>13</v>
       </c>
-      <c r="D12" s="11" t="str">
+      <c r="D12" s="48" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$D:$D,Sheet1!$C:$C,$C12,Sheet1!$B:$B,D$1,Sheet1!$A:$A,$A12)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$E:$E,Sheet1!$C:$C,$C12,Sheet1!$B:$B,D$1,Sheet1!$A:$A,$A12)*100,2),"0.00")</f>
-        <v>49.3863 ± 24.31</v>
-      </c>
-      <c r="E12" s="8" t="str">
+        <v>58.4801 ± 23.33</v>
+      </c>
+      <c r="E12" s="30" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$F:$F,Sheet1!$C:$C,$C12,Sheet1!$B:$B,E$1,Sheet1!$A:$A,$A12)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$G:$G,Sheet1!$C:$C,$C12,Sheet1!$B:$B,E$1,Sheet1!$A:$A,$A12)*100,2),"0.00")</f>
-        <v>13.5250 ± 20.07</v>
-      </c>
-      <c r="F12" s="8" t="str">
+        <v>28.3444 ± 29.88</v>
+      </c>
+      <c r="F12" s="41" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$H:$H,Sheet1!$C:$C,$C12,Sheet1!$B:$B,F$1,Sheet1!$A:$A,$A12)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$I:$I,Sheet1!$C:$C,$C12,Sheet1!$B:$B,F$1,Sheet1!$A:$A,$A12)*100,2),"0.00")</f>
-        <v>20.1772 ± 33.59</v>
-      </c>
-      <c r="G12" s="12" t="str">
+        <v>40.2713 ± 43.35</v>
+      </c>
+      <c r="G12" s="31" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$J:$J,Sheet1!$C:$C,$C12,Sheet1!$B:$B,G$1,Sheet1!$A:$A,$A12)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$K:$K,Sheet1!$C:$C,$C12,Sheet1!$B:$B,G$1,Sheet1!$A:$A,$A12)*100,2),"0.00")</f>
-        <v>15.3618 ± 26.43</v>
-      </c>
-      <c r="H12" s="11" t="str">
+        <v>27.9596 ± 33.27</v>
+      </c>
+      <c r="H12" s="29" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$D:$D,Sheet1!$C:$C,$C12,Sheet1!$B:$B,H$1,Sheet1!$A:$A,$A12)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$E:$E,Sheet1!$C:$C,$C12,Sheet1!$B:$B,H$1,Sheet1!$A:$A,$A12)*100,2),"0.00")</f>
-        <v>50.6460 ± 27.04</v>
-      </c>
-      <c r="I12" s="8" t="str">
+        <v>59.0126 ± 22.38</v>
+      </c>
+      <c r="I12" s="30" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$F:$F,Sheet1!$C:$C,$C12,Sheet1!$B:$B,I$1,Sheet1!$A:$A,$A12)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$G:$G,Sheet1!$C:$C,$C12,Sheet1!$B:$B,I$1,Sheet1!$A:$A,$A12)*100,2),"0.00")</f>
-        <v>13.8803 ± 22.00</v>
-      </c>
-      <c r="J12" s="8" t="str">
+        <v>22.6743 ± 25.99</v>
+      </c>
+      <c r="J12" s="30" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$H:$H,Sheet1!$C:$C,$C12,Sheet1!$B:$B,J$1,Sheet1!$A:$A,$A12)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$I:$I,Sheet1!$C:$C,$C12,Sheet1!$B:$B,J$1,Sheet1!$A:$A,$A12)*100,2),"0.00")</f>
-        <v>15.9690 ± 27.43</v>
-      </c>
-      <c r="K12" s="12" t="str">
+        <v>35.5426 ± 42.01</v>
+      </c>
+      <c r="K12" s="31" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$J:$J,Sheet1!$C:$C,$C12,Sheet1!$B:$B,K$1,Sheet1!$A:$A,$A12)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$K:$K,Sheet1!$C:$C,$C12,Sheet1!$B:$B,K$1,Sheet1!$A:$A,$A12)*100,2),"0.00")</f>
-        <v>17.5581 ± 30.41</v>
-      </c>
-      <c r="L12" s="11" t="str">
+        <v>19.3217 ± 23.78</v>
+      </c>
+      <c r="L12" s="48" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$D:$D,Sheet1!$C:$C,$C12,Sheet1!$B:$B,L$1,Sheet1!$A:$A,$A12)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$E:$E,Sheet1!$C:$C,$C12,Sheet1!$B:$B,L$1,Sheet1!$A:$A,$A12)*100,2),"0.00")</f>
-        <v>52.7132 ± 26.80</v>
-      </c>
-      <c r="M12" s="8" t="str">
+        <v>58.8778 ± 22.35</v>
+      </c>
+      <c r="M12" s="30" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$F:$F,Sheet1!$C:$C,$C12,Sheet1!$B:$B,M$1,Sheet1!$A:$A,$A12)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$G:$G,Sheet1!$C:$C,$C12,Sheet1!$B:$B,M$1,Sheet1!$A:$A,$A12)*100,2),"0.00")</f>
-        <v>13.7015 ± 22.95</v>
-      </c>
-      <c r="N12" s="8" t="str">
+        <v>24.3065 ± 29.59</v>
+      </c>
+      <c r="N12" s="30" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$H:$H,Sheet1!$C:$C,$C12,Sheet1!$B:$B,N$1,Sheet1!$A:$A,$A12)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$I:$I,Sheet1!$C:$C,$C12,Sheet1!$B:$B,N$1,Sheet1!$A:$A,$A12)*100,2),"0.00")</f>
-        <v>18.0454 ± 31.08</v>
-      </c>
-      <c r="O12" s="12" t="str">
+        <v>36.8992 ± 43.63</v>
+      </c>
+      <c r="O12" s="31" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$J:$J,Sheet1!$C:$C,$C12,Sheet1!$B:$B,O$1,Sheet1!$A:$A,$A12)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$K:$K,Sheet1!$C:$C,$C12,Sheet1!$B:$B,O$1,Sheet1!$A:$A,$A12)*100,2),"0.00")</f>
-        <v>16.8051 ± 30.96</v>
+        <v>22.0266 ± 30.41</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A13" s="27" t="s">
+      <c r="A13" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="B13" s="35"/>
+      <c r="B13" s="15"/>
       <c r="C13" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D13" s="13" t="str">
+      <c r="D13" s="6" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$D:$D,Sheet1!$C:$C,$C13,Sheet1!$B:$B,D$1,Sheet1!$A:$A,$A13)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$E:$E,Sheet1!$C:$C,$C13,Sheet1!$B:$B,D$1,Sheet1!$A:$A,$A13)*100,2),"0.00")</f>
-        <v>46.3501 ± 23.30</v>
-      </c>
-      <c r="E13" s="6" t="str">
+        <v>58.1792 ± 19.83</v>
+      </c>
+      <c r="E13" s="4" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$F:$F,Sheet1!$C:$C,$C13,Sheet1!$B:$B,E$1,Sheet1!$A:$A,$A13)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$G:$G,Sheet1!$C:$C,$C13,Sheet1!$B:$B,E$1,Sheet1!$A:$A,$A13)*100,2),"0.00")</f>
-        <v>24.3187 ± 27.48</v>
-      </c>
-      <c r="F13" s="7" t="str">
+        <v>31.5988 ± 29.71</v>
+      </c>
+      <c r="F13" s="5" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$H:$H,Sheet1!$C:$C,$C13,Sheet1!$B:$B,F$1,Sheet1!$A:$A,$A13)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$I:$I,Sheet1!$C:$C,$C13,Sheet1!$B:$B,F$1,Sheet1!$A:$A,$A13)*100,2),"0.00")</f>
-        <v>30.4134 ± 37.62</v>
-      </c>
-      <c r="G13" s="19" t="str">
+        <v>41.3455 ± 40.48</v>
+      </c>
+      <c r="G13" s="9" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$J:$J,Sheet1!$C:$C,$C13,Sheet1!$B:$B,G$1,Sheet1!$A:$A,$A13)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$K:$K,Sheet1!$C:$C,$C13,Sheet1!$B:$B,G$1,Sheet1!$A:$A,$A13)*100,2),"0.00")</f>
-        <v>29.0882 ± 35.92</v>
-      </c>
-      <c r="H13" s="13" t="str">
+        <v>35.3267 ± 37.06</v>
+      </c>
+      <c r="H13" s="8" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$D:$D,Sheet1!$C:$C,$C13,Sheet1!$B:$B,H$1,Sheet1!$A:$A,$A13)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$E:$E,Sheet1!$C:$C,$C13,Sheet1!$B:$B,H$1,Sheet1!$A:$A,$A13)*100,2),"0.00")</f>
-        <v>39.5349 ± 21.74</v>
-      </c>
-      <c r="I13" s="6" t="str">
+        <v>60.1827 ± 18.34</v>
+      </c>
+      <c r="I13" s="4" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$F:$F,Sheet1!$C:$C,$C13,Sheet1!$B:$B,I$1,Sheet1!$A:$A,$A13)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$G:$G,Sheet1!$C:$C,$C13,Sheet1!$B:$B,I$1,Sheet1!$A:$A,$A13)*100,2),"0.00")</f>
-        <v>23.6351 ± 24.68</v>
-      </c>
-      <c r="J13" s="7" t="str">
+        <v>33.9054 ± 30.45</v>
+      </c>
+      <c r="J13" s="4" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$H:$H,Sheet1!$C:$C,$C13,Sheet1!$B:$B,J$1,Sheet1!$A:$A,$A13)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$I:$I,Sheet1!$C:$C,$C13,Sheet1!$B:$B,J$1,Sheet1!$A:$A,$A13)*100,2),"0.00")</f>
-        <v>27.8904 ± 31.98</v>
-      </c>
-      <c r="K13" s="19" t="str">
+        <v>45.8140 ± 42.18</v>
+      </c>
+      <c r="K13" s="9" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$J:$J,Sheet1!$C:$C,$C13,Sheet1!$B:$B,K$1,Sheet1!$A:$A,$A13)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$K:$K,Sheet1!$C:$C,$C13,Sheet1!$B:$B,K$1,Sheet1!$A:$A,$A13)*100,2),"0.00")</f>
-        <v>31.4793 ± 35.49</v>
-      </c>
-      <c r="L13" s="13" t="str">
+        <v>32.2730 ± 31.69</v>
+      </c>
+      <c r="L13" s="6" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$D:$D,Sheet1!$C:$C,$C13,Sheet1!$B:$B,L$1,Sheet1!$A:$A,$A13)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$E:$E,Sheet1!$C:$C,$C13,Sheet1!$B:$B,L$1,Sheet1!$A:$A,$A13)*100,2),"0.00")</f>
-        <v>44.9612 ± 23.59</v>
-      </c>
-      <c r="M13" s="7" t="str">
+        <v>57.6689 ± 16.44</v>
+      </c>
+      <c r="M13" s="4" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$F:$F,Sheet1!$C:$C,$C13,Sheet1!$B:$B,M$1,Sheet1!$A:$A,$A13)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$G:$G,Sheet1!$C:$C,$C13,Sheet1!$B:$B,M$1,Sheet1!$A:$A,$A13)*100,2),"0.00")</f>
-        <v>20.0456 ± 25.79</v>
-      </c>
-      <c r="N13" s="7" t="str">
+        <v>29.3631 ± 27.40</v>
+      </c>
+      <c r="N13" s="4" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$H:$H,Sheet1!$C:$C,$C13,Sheet1!$B:$B,N$1,Sheet1!$A:$A,$A13)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$I:$I,Sheet1!$C:$C,$C13,Sheet1!$B:$B,N$1,Sheet1!$A:$A,$A13)*100,2),"0.00")</f>
-        <v>25.3036 ± 35.11</v>
-      </c>
-      <c r="O13" s="14" t="str">
+        <v>43.0620 ± 41.38</v>
+      </c>
+      <c r="O13" s="9" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$J:$J,Sheet1!$C:$C,$C13,Sheet1!$B:$B,O$1,Sheet1!$A:$A,$A13)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$K:$K,Sheet1!$C:$C,$C13,Sheet1!$B:$B,O$1,Sheet1!$A:$A,$A13)*100,2),"0.00")</f>
-        <v>24.0818 ± 33.31</v>
+        <v>29.8588 ± 32.35</v>
       </c>
     </row>
     <row r="14" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="27" t="s">
+      <c r="A14" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="B14" s="36"/>
-      <c r="C14" s="21" t="s">
+      <c r="B14" s="16"/>
+      <c r="C14" s="43" t="s">
         <v>14</v>
       </c>
-      <c r="D14" s="15" t="str">
+      <c r="D14" s="47" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$D:$D,Sheet1!$C:$C,$C14,Sheet1!$B:$B,D$1,Sheet1!$A:$A,$A14)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$E:$E,Sheet1!$C:$C,$C14,Sheet1!$B:$B,D$1,Sheet1!$A:$A,$A14)*100,2),"0.00")</f>
-        <v>45.5426 ± 21.07</v>
-      </c>
-      <c r="E14" s="16" t="str">
+        <v>58.1432 ± 21.39</v>
+      </c>
+      <c r="E14" s="45" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$F:$F,Sheet1!$C:$C,$C14,Sheet1!$B:$B,E$1,Sheet1!$A:$A,$A14)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$G:$G,Sheet1!$C:$C,$C14,Sheet1!$B:$B,E$1,Sheet1!$A:$A,$A14)*100,2),"0.00")</f>
-        <v>16.3930 ± 19.49</v>
-      </c>
-      <c r="F14" s="16" t="str">
+        <v>17.9070 ± 23.14</v>
+      </c>
+      <c r="F14" s="45" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$H:$H,Sheet1!$C:$C,$C14,Sheet1!$B:$B,F$1,Sheet1!$A:$A,$A14)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$I:$I,Sheet1!$C:$C,$C14,Sheet1!$B:$B,F$1,Sheet1!$A:$A,$A14)*100,2),"0.00")</f>
-        <v>24.6770 ± 34.08</v>
-      </c>
-      <c r="G14" s="17" t="str">
+        <v>30.2326 ± 40.07</v>
+      </c>
+      <c r="G14" s="46" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$J:$J,Sheet1!$C:$C,$C14,Sheet1!$B:$B,G$1,Sheet1!$A:$A,$A14)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$K:$K,Sheet1!$C:$C,$C14,Sheet1!$B:$B,G$1,Sheet1!$A:$A,$A14)*100,2),"0.00")</f>
-        <v>18.0805 ± 25.12</v>
-      </c>
-      <c r="H14" s="24" t="str">
+        <v>16.5615 ± 25.54</v>
+      </c>
+      <c r="H14" s="47" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$D:$D,Sheet1!$C:$C,$C14,Sheet1!$B:$B,H$1,Sheet1!$A:$A,$A14)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$E:$E,Sheet1!$C:$C,$C14,Sheet1!$B:$B,H$1,Sheet1!$A:$A,$A14)*100,2),"0.00")</f>
-        <v>54.5220 ± 22.71</v>
-      </c>
-      <c r="I14" s="16" t="str">
+        <v>58.2614 ± 23.70</v>
+      </c>
+      <c r="I14" s="45" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$F:$F,Sheet1!$C:$C,$C14,Sheet1!$B:$B,I$1,Sheet1!$A:$A,$A14)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$G:$G,Sheet1!$C:$C,$C14,Sheet1!$B:$B,I$1,Sheet1!$A:$A,$A14)*100,2),"0.00")</f>
-        <v>23.3936 ± 26.08</v>
-      </c>
-      <c r="J14" s="25" t="str">
+        <v>17.8387 ± 22.07</v>
+      </c>
+      <c r="J14" s="45" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$H:$H,Sheet1!$C:$C,$C14,Sheet1!$B:$B,J$1,Sheet1!$A:$A,$A14)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$I:$I,Sheet1!$C:$C,$C14,Sheet1!$B:$B,J$1,Sheet1!$A:$A,$A14)*100,2),"0.00")</f>
-        <v>34.2636 ± 39.35</v>
-      </c>
-      <c r="K14" s="17" t="str">
+        <v>31.3953 ± 40.06</v>
+      </c>
+      <c r="K14" s="46" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$J:$J,Sheet1!$C:$C,$C14,Sheet1!$B:$B,K$1,Sheet1!$A:$A,$A14)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$K:$K,Sheet1!$C:$C,$C14,Sheet1!$B:$B,K$1,Sheet1!$A:$A,$A14)*100,2),"0.00")</f>
-        <v>25.5962 ± 33.76</v>
-      </c>
-      <c r="L14" s="15" t="str">
+        <v>16.7386 ± 25.32</v>
+      </c>
+      <c r="L14" s="47" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$D:$D,Sheet1!$C:$C,$C14,Sheet1!$B:$B,L$1,Sheet1!$A:$A,$A14)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$E:$E,Sheet1!$C:$C,$C14,Sheet1!$B:$B,L$1,Sheet1!$A:$A,$A14)*100,2),"0.00")</f>
-        <v>50.6460 ± 22.90</v>
-      </c>
-      <c r="M14" s="16" t="str">
+        <v>56.6205 ± 23.59</v>
+      </c>
+      <c r="M14" s="45" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$F:$F,Sheet1!$C:$C,$C14,Sheet1!$B:$B,M$1,Sheet1!$A:$A,$A14)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$G:$G,Sheet1!$C:$C,$C14,Sheet1!$B:$B,M$1,Sheet1!$A:$A,$A14)*100,2),"0.00")</f>
-        <v>20.6126 ± 22.72</v>
-      </c>
-      <c r="N14" s="16" t="str">
+        <v>17.7058 ± 22.32</v>
+      </c>
+      <c r="N14" s="45" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$H:$H,Sheet1!$C:$C,$C14,Sheet1!$B:$B,N$1,Sheet1!$A:$A,$A14)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$I:$I,Sheet1!$C:$C,$C14,Sheet1!$B:$B,N$1,Sheet1!$A:$A,$A14)*100,2),"0.00")</f>
-        <v>26.0908 ± 32.89</v>
-      </c>
-      <c r="O14" s="17" t="str">
+        <v>35.5426 ± 44.54</v>
+      </c>
+      <c r="O14" s="46" t="str">
         <f>TEXT(ROUND(SUMIFS(Sheet1!$J:$J,Sheet1!$C:$C,$C14,Sheet1!$B:$B,O$1,Sheet1!$A:$A,$A14)*100,4),"0.0000") &amp; " ± " &amp; TEXT(ROUND(SUMIFS(Sheet1!$K:$K,Sheet1!$C:$C,$C14,Sheet1!$B:$B,O$1,Sheet1!$A:$A,$A14)*100,2),"0.00")</f>
-        <v>24.6558 ± 31.85</v>
+        <v>15.4568 ± 22.60</v>
       </c>
     </row>
   </sheetData>
